--- a/data/pack/eu/maiz.xlsx
+++ b/data/pack/eu/maiz.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K550"/>
+  <dimension ref="A1:K551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -30684,6 +30684,61 @@
         </is>
       </c>
       <c r="K550" t="inlineStr">
+        <is>
+          <t>Source: European Commission (Agri-food data portal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>maiz</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Maíz</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>259</v>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>tonelada</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>European Commission — Agri-food Data Portal (DG AGRI)</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>EU-REUSE-2011-833</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
         <is>
           <t>Source: European Commission (Agri-food data portal)</t>
         </is>
@@ -30787,7 +30842,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -30798,7 +30853,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="9">
@@ -30893,7 +30948,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>

--- a/data/pack/eu/maiz.xlsx
+++ b/data/pack/eu/maiz.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K551"/>
+  <dimension ref="A1:K552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -30739,6 +30739,61 @@
         </is>
       </c>
       <c r="K551" t="inlineStr">
+        <is>
+          <t>Source: European Commission (Agri-food data portal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>maiz</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Maíz</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>259</v>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>tonelada</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>European Commission — Agri-food Data Portal (DG AGRI)</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>EU-REUSE-2011-833</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
         <is>
           <t>Source: European Commission (Agri-food data portal)</t>
         </is>
@@ -30842,7 +30897,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -30853,7 +30908,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="9">
@@ -30948,7 +31003,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
